--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11914,6 +11914,105 @@
         <v>344.77</v>
       </c>
       <c r="I350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="C351" t="n">
+        <v>268.13</v>
+      </c>
+      <c r="D351" t="n">
+        <v>316.07</v>
+      </c>
+      <c r="E351" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="F351" t="n">
+        <v>330.73</v>
+      </c>
+      <c r="G351" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="H351" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>198.66</v>
+      </c>
+      <c r="C352" t="n">
+        <v>249.63</v>
+      </c>
+      <c r="D352" t="n">
+        <v>310.86</v>
+      </c>
+      <c r="E352" t="n">
+        <v>318.15</v>
+      </c>
+      <c r="F352" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="G352" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="H352" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>196.16</v>
+      </c>
+      <c r="C353" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="D353" t="n">
+        <v>308.39</v>
+      </c>
+      <c r="E353" t="n">
+        <v>318.62</v>
+      </c>
+      <c r="F353" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="G353" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="H353" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="I353" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11930,7 +12029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15783,6 +15882,36 @@
       </c>
       <c r="B385" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -15951,28 +16080,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2284394718801576</v>
+        <v>0.08162155223465262</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004908436412907058</v>
+        <v>6.305718022880935e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>65.3249790570864</v>
+        <v>65.40437588372887</v>
       </c>
       <c r="N2" t="n">
-        <v>5222.074830997608</v>
+        <v>5233.231512524325</v>
       </c>
       <c r="O2" t="n">
-        <v>72.26392482419985</v>
+        <v>72.34107762899531</v>
       </c>
       <c r="P2" t="n">
-        <v>273.9377933572414</v>
+        <v>275.7234487625193</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16029,28 +16158,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.421910668929792</v>
+        <v>-1.523726394418981</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04691027988831253</v>
+        <v>0.05352625929139665</v>
       </c>
       <c r="M3" t="n">
-        <v>33.50881345685971</v>
+        <v>33.93095473103093</v>
       </c>
       <c r="N3" t="n">
-        <v>2066.62401734649</v>
+        <v>2081.89254144768</v>
       </c>
       <c r="O3" t="n">
-        <v>45.4601365742173</v>
+        <v>45.6277606446742</v>
       </c>
       <c r="P3" t="n">
-        <v>350.6006601983499</v>
+        <v>351.8111935649654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16107,28 +16236,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5479902600594045</v>
+        <v>0.4863000916483562</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1418526326711842</v>
+        <v>0.1049264401927802</v>
       </c>
       <c r="M4" t="n">
-        <v>7.503013572484476</v>
+        <v>7.787301613663816</v>
       </c>
       <c r="N4" t="n">
-        <v>92.59633145849739</v>
+        <v>103.6434603293335</v>
       </c>
       <c r="O4" t="n">
-        <v>9.62269876170388</v>
+        <v>10.18054322368573</v>
       </c>
       <c r="P4" t="n">
-        <v>334.5968907533876</v>
+        <v>335.3243114354938</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16185,28 +16314,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8001924191857707</v>
+        <v>0.7572567415367546</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2102151374372496</v>
+        <v>0.1879868487276973</v>
       </c>
       <c r="M5" t="n">
-        <v>8.845311428591028</v>
+        <v>9.024527050956461</v>
       </c>
       <c r="N5" t="n">
-        <v>122.3295006070522</v>
+        <v>126.9622703597373</v>
       </c>
       <c r="O5" t="n">
-        <v>11.06026675117071</v>
+        <v>11.26775356314369</v>
       </c>
       <c r="P5" t="n">
-        <v>323.2474501407577</v>
+        <v>323.7540188748173</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16263,28 +16392,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6716064633094637</v>
+        <v>0.6314238914543346</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2960085140120258</v>
+        <v>0.2570815822892907</v>
       </c>
       <c r="M6" t="n">
-        <v>5.473888555504208</v>
+        <v>5.675024938753572</v>
       </c>
       <c r="N6" t="n">
-        <v>54.54946003574159</v>
+        <v>59.0561280640957</v>
       </c>
       <c r="O6" t="n">
-        <v>7.385760626756163</v>
+        <v>7.68479850510706</v>
       </c>
       <c r="P6" t="n">
-        <v>337.3052521227647</v>
+        <v>337.7793339159958</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16341,28 +16470,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6343213645404142</v>
+        <v>0.5978481540844969</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3019788865579059</v>
+        <v>0.2643146250927839</v>
       </c>
       <c r="M7" t="n">
-        <v>5.014364776687208</v>
+        <v>5.179812218592835</v>
       </c>
       <c r="N7" t="n">
-        <v>47.2942318216949</v>
+        <v>50.99240570907518</v>
       </c>
       <c r="O7" t="n">
-        <v>6.877080181421102</v>
+        <v>7.140896702030858</v>
       </c>
       <c r="P7" t="n">
-        <v>347.9238732728024</v>
+        <v>348.3541785784624</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16419,28 +16548,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6210035167372553</v>
+        <v>0.5760520219691905</v>
       </c>
       <c r="J8" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1929276124154942</v>
+        <v>0.162662828864105</v>
       </c>
       <c r="M8" t="n">
-        <v>6.25284604104773</v>
+        <v>6.460666129345594</v>
       </c>
       <c r="N8" t="n">
-        <v>82.03586022109218</v>
+        <v>87.55647096100998</v>
       </c>
       <c r="O8" t="n">
-        <v>9.057364971176339</v>
+        <v>9.357161479904574</v>
       </c>
       <c r="P8" t="n">
-        <v>352.4864436301465</v>
+        <v>353.0167924679644</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16478,7 +16607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32779,6 +32908,147 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-45.80910960996664,170.74225664597725</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-45.809943588287524,170.7426592681749</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-45.810714297734165,170.74289361352658</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-45.81132798863818,170.74270252727786</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-45.81194943958214,170.74253615233837</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-45.812582329251306,170.74245968738913</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-45.81319940124411,170.74236657046413</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-45.809096121636536,170.74221467895546</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-45.80987735060949,170.74244091180068</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-45.81069902757419,170.74283023895708</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-45.81132530702295,170.7426910573114</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-45.811951586645854,170.74254557145966</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-45.81258591845553,170.74248582127512</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-45.81319940124411,170.74236657046413</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-45.80908672864011,170.7421854540222</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-45.809826401025596,170.74227295479955</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-45.81069178815805,170.74280019382823</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-45.811326647830704,170.7426967922945</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-45.81194868671545,170.7425328495298</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-45.81258392445392,170.7424713024491</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-45.81319896714613,170.74236172080504</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12013,6 +12013,72 @@
         <v>341.56</v>
       </c>
       <c r="I353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>194.41</v>
+      </c>
+      <c r="C354" t="n">
+        <v>236.38</v>
+      </c>
+      <c r="D354" t="n">
+        <v>308.73</v>
+      </c>
+      <c r="E354" t="n">
+        <v>317.48</v>
+      </c>
+      <c r="F354" t="n">
+        <v>329.59</v>
+      </c>
+      <c r="G354" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="H354" t="n">
+        <v>340.13</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>193.66</v>
+      </c>
+      <c r="C355" t="n">
+        <v>236.38</v>
+      </c>
+      <c r="D355" t="n">
+        <v>309.4</v>
+      </c>
+      <c r="E355" t="n">
+        <v>317.52</v>
+      </c>
+      <c r="F355" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="G355" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="H355" t="n">
+        <v>340.26</v>
+      </c>
+      <c r="I355" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12029,7 +12095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B388"/>
+  <dimension ref="A1:B390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15912,6 +15978,26 @@
       </c>
       <c r="B388" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -16080,28 +16166,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08162155223465262</v>
+        <v>-0.0187682057698924</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>6.305718022880935e-05</v>
+        <v>3.344960269324737e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>65.40437588372887</v>
+        <v>65.47198928581807</v>
       </c>
       <c r="N2" t="n">
-        <v>5233.231512524325</v>
+        <v>5243.765623917402</v>
       </c>
       <c r="O2" t="n">
-        <v>72.34107762899531</v>
+        <v>72.41384966922696</v>
       </c>
       <c r="P2" t="n">
-        <v>275.7234487625193</v>
+        <v>276.9489934401872</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16158,28 +16244,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.523726394418981</v>
+        <v>-1.60530332594537</v>
       </c>
       <c r="J3" t="n">
+        <v>354</v>
+      </c>
+      <c r="K3" t="n">
         <v>352</v>
       </c>
-      <c r="K3" t="n">
-        <v>350</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05352625929139665</v>
+        <v>0.0588469056472265</v>
       </c>
       <c r="M3" t="n">
-        <v>33.93095473103093</v>
+        <v>34.30836137211557</v>
       </c>
       <c r="N3" t="n">
-        <v>2081.89254144768</v>
+        <v>2100.970227786216</v>
       </c>
       <c r="O3" t="n">
-        <v>45.6277606446742</v>
+        <v>45.83634178014445</v>
       </c>
       <c r="P3" t="n">
-        <v>351.8111935649654</v>
+        <v>352.784419818618</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16236,28 +16322,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4863000916483562</v>
+        <v>0.4435409318752309</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1049264401927802</v>
+        <v>0.08337807314836754</v>
       </c>
       <c r="M4" t="n">
-        <v>7.787301613663816</v>
+        <v>8.000446430044166</v>
       </c>
       <c r="N4" t="n">
-        <v>103.6434603293335</v>
+        <v>111.6917544046919</v>
       </c>
       <c r="O4" t="n">
-        <v>10.18054322368573</v>
+        <v>10.56843197473929</v>
       </c>
       <c r="P4" t="n">
-        <v>335.3243114354938</v>
+        <v>335.8303239919402</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16314,28 +16400,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7572567415367546</v>
+        <v>0.7282842026902925</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1879868487276973</v>
+        <v>0.1734907661693298</v>
       </c>
       <c r="M5" t="n">
-        <v>9.024527050956461</v>
+        <v>9.14836573824134</v>
       </c>
       <c r="N5" t="n">
-        <v>126.9622703597373</v>
+        <v>130.1951130339494</v>
       </c>
       <c r="O5" t="n">
-        <v>11.26775356314369</v>
+        <v>11.41030731549108</v>
       </c>
       <c r="P5" t="n">
-        <v>323.7540188748173</v>
+        <v>324.0971077107474</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16392,28 +16478,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6314238914543346</v>
+        <v>0.6037246394524929</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2570815822892907</v>
+        <v>0.2315295530853758</v>
       </c>
       <c r="M6" t="n">
-        <v>5.675024938753572</v>
+        <v>5.822062105968405</v>
       </c>
       <c r="N6" t="n">
-        <v>59.0561280640957</v>
+        <v>62.33329679616547</v>
       </c>
       <c r="O6" t="n">
-        <v>7.68479850510706</v>
+        <v>7.895143874317014</v>
       </c>
       <c r="P6" t="n">
-        <v>337.7793339159958</v>
+        <v>338.1073502739522</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16470,28 +16556,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5978481540844969</v>
+        <v>0.5737517133819503</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2643146250927839</v>
+        <v>0.2409364928110446</v>
       </c>
       <c r="M7" t="n">
-        <v>5.179812218592835</v>
+        <v>5.290726834747033</v>
       </c>
       <c r="N7" t="n">
-        <v>50.99240570907518</v>
+        <v>53.43737030703738</v>
       </c>
       <c r="O7" t="n">
-        <v>7.140896702030858</v>
+        <v>7.31008688778987</v>
       </c>
       <c r="P7" t="n">
-        <v>348.3541785784624</v>
+        <v>348.63953304216</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16548,28 +16634,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5760520219691905</v>
+        <v>0.5452495992426971</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.162662828864105</v>
+        <v>0.1433697899108517</v>
       </c>
       <c r="M8" t="n">
-        <v>6.460666129345594</v>
+        <v>6.60656601261638</v>
       </c>
       <c r="N8" t="n">
-        <v>87.55647096100998</v>
+        <v>91.52674256303652</v>
       </c>
       <c r="O8" t="n">
-        <v>9.357161479904574</v>
+        <v>9.566960988894881</v>
       </c>
       <c r="P8" t="n">
-        <v>353.0167924679644</v>
+        <v>353.3815495838029</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16607,7 +16693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33049,6 +33135,100 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-45.80908015353824,170.74216499657487</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-45.80982990985923,170.7422845217509</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-45.810692784677336,170.7428043295945</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-45.8113233956582,170.74268288191047</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-45.81194626081106,170.74252220714723</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-45.81258392445392,170.7424713024491</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-45.81319733356504,170.74234347077285</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-45.809077335636346,170.74215622909895</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-45.80982990985923,170.7422845217509</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-45.81069474840608,170.74281247948724</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-45.811323509769544,170.7426833699941</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-45.81194467142491,170.74251523455226</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-45.812582537321276,170.74246120239692</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-45.81319748207253,170.74234512986664</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I355"/>
+  <dimension ref="A1:I356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12061,7 +12061,7 @@
         <v>193.66</v>
       </c>
       <c r="C355" t="n">
-        <v>236.38</v>
+        <v>244.4</v>
       </c>
       <c r="D355" t="n">
         <v>309.4</v>
@@ -12079,6 +12079,39 @@
         <v>340.26</v>
       </c>
       <c r="I355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>169.52</v>
+      </c>
+      <c r="C356" t="n">
+        <v>231.46</v>
+      </c>
+      <c r="D356" t="n">
+        <v>306.62</v>
+      </c>
+      <c r="E356" t="n">
+        <v>316.34</v>
+      </c>
+      <c r="F356" t="n">
+        <v>327.77</v>
+      </c>
+      <c r="G356" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="H356" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="I356" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12095,7 +12128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B390"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15998,6 +16031,16 @@
       </c>
       <c r="B390" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -16166,28 +16209,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0187682057698924</v>
+        <v>-0.08297593225917331</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>3.344960269324737e-06</v>
+        <v>6.531437227375037e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>65.47198928581807</v>
+        <v>65.5675571530998</v>
       </c>
       <c r="N2" t="n">
-        <v>5243.765623917402</v>
+        <v>5262.784406084101</v>
       </c>
       <c r="O2" t="n">
-        <v>72.41384966922696</v>
+        <v>72.54505087243444</v>
       </c>
       <c r="P2" t="n">
-        <v>276.9489934401872</v>
+        <v>277.7370378986348</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16244,28 +16287,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.60530332594537</v>
+        <v>-1.643791358231957</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0588469056472265</v>
+        <v>0.06146208531155473</v>
       </c>
       <c r="M3" t="n">
-        <v>34.30836137211557</v>
+        <v>34.47729501246673</v>
       </c>
       <c r="N3" t="n">
-        <v>2100.970227786216</v>
+        <v>2108.936316695707</v>
       </c>
       <c r="O3" t="n">
-        <v>45.83634178014445</v>
+        <v>45.92315664994848</v>
       </c>
       <c r="P3" t="n">
-        <v>352.784419818618</v>
+        <v>353.246200141409</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16322,28 +16365,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4435409318752309</v>
+        <v>0.4210661821753429</v>
       </c>
       <c r="J4" t="n">
+        <v>355</v>
+      </c>
+      <c r="K4" t="n">
         <v>354</v>
       </c>
-      <c r="K4" t="n">
-        <v>353</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.08337807314836754</v>
+        <v>0.07325810647554409</v>
       </c>
       <c r="M4" t="n">
-        <v>8.000446430044166</v>
+        <v>8.115458303593401</v>
       </c>
       <c r="N4" t="n">
-        <v>111.6917544046919</v>
+        <v>116.1368638096514</v>
       </c>
       <c r="O4" t="n">
-        <v>10.56843197473929</v>
+        <v>10.77668148409572</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8303239919402</v>
+        <v>336.0977026774614</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16400,28 +16443,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7282842026902925</v>
+        <v>0.7132981369676705</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1734907661693298</v>
+        <v>0.1661308965731155</v>
       </c>
       <c r="M5" t="n">
-        <v>9.14836573824134</v>
+        <v>9.213412285950225</v>
       </c>
       <c r="N5" t="n">
-        <v>130.1951130339494</v>
+        <v>131.9375957296433</v>
       </c>
       <c r="O5" t="n">
-        <v>11.41030731549108</v>
+        <v>11.48640917474401</v>
       </c>
       <c r="P5" t="n">
-        <v>324.0971077107474</v>
+        <v>324.2755062748824</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16478,28 +16521,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6037246394524929</v>
+        <v>0.5891743901856777</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2315295530853758</v>
+        <v>0.2184898931461727</v>
       </c>
       <c r="M6" t="n">
-        <v>5.822062105968405</v>
+        <v>5.904378252747542</v>
       </c>
       <c r="N6" t="n">
-        <v>62.33329679616547</v>
+        <v>64.1460444915505</v>
       </c>
       <c r="O6" t="n">
-        <v>7.895143874317014</v>
+        <v>8.009122579380996</v>
       </c>
       <c r="P6" t="n">
-        <v>338.1073502739522</v>
+        <v>338.2805607499405</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16556,28 +16599,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5737517133819503</v>
+        <v>0.5608382136876359</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2409364928110446</v>
+        <v>0.2285419821186175</v>
       </c>
       <c r="M7" t="n">
-        <v>5.290726834747033</v>
+        <v>5.352722318082602</v>
       </c>
       <c r="N7" t="n">
-        <v>53.43737030703738</v>
+        <v>54.85300378331725</v>
       </c>
       <c r="O7" t="n">
-        <v>7.31008688778987</v>
+        <v>7.406281373490832</v>
       </c>
       <c r="P7" t="n">
-        <v>348.63953304216</v>
+        <v>348.793259166552</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16634,28 +16677,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5452495992426971</v>
+        <v>0.5289819701346921</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1433697899108517</v>
+        <v>0.1335950226040242</v>
       </c>
       <c r="M8" t="n">
-        <v>6.60656601261638</v>
+        <v>6.684418117490406</v>
       </c>
       <c r="N8" t="n">
-        <v>91.52674256303652</v>
+        <v>93.7543253310256</v>
       </c>
       <c r="O8" t="n">
-        <v>9.566960988894881</v>
+        <v>9.682681722076049</v>
       </c>
       <c r="P8" t="n">
-        <v>353.3815495838029</v>
+        <v>353.5752042579826</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16693,7 +16736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I355"/>
+  <dimension ref="A1:I356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33195,7 +33238,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-45.80982990985923,170.7422845217509</t>
+          <t>-45.809858624964804,170.74237918195982</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -33224,6 +33267,53 @@
         </is>
       </c>
       <c r="I355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-45.80898663641603,170.74187403375777</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-45.809812294070674,170.74222645094895</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-45.81068660039353,170.74277866351815</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-45.811320143484025,170.74266897152813</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-45.811941185927466,170.74249994377527</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-45.81258010983703,170.74244352730682</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-45.81319525445764,170.74232024346085</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
